--- a/data/reunioes.xlsx
+++ b/data/reunioes.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,106 +469,6 @@
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>melembre</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>matheus</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rose</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>melembre concob</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>46087</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>etstes</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>46087</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/reunioes.xlsx
+++ b/data/reunioes.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +473,38 @@
           <t>Observações</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>testes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
